--- a/тест-кейсы.xlsx
+++ b/тест-кейсы.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ivankosarev/Documents/ВУЗ/Программная инженерия/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7685A2E-FD2C-304C-8796-02985610AD7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B49116-4BF6-2041-B6A2-217197EFD47A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="43">
   <si>
     <t>Номер кейса</t>
   </si>
@@ -141,6 +141,24 @@
   </si>
   <si>
     <t>1.Нажать на экран два раза, удержать и повести вверх</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>Масштаб карты не изменился</t>
+  </si>
+  <si>
+    <t>Проверка работы кнопки "+" на клавиатуре для увеличения масштаба</t>
+  </si>
+  <si>
+    <t>Проверка работы кнопки "-" на клавиатуре для уменьшения масштаба</t>
+  </si>
+  <si>
+    <t>Проверка работы тачскрина для уменьшения масштаба</t>
+  </si>
+  <si>
+    <t>Проверка работы тачскрина для увеличения масштаба</t>
   </si>
 </sst>
 </file>
@@ -523,7 +541,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>8</v>
@@ -535,13 +553,13 @@
         <v>10</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>25</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="96" x14ac:dyDescent="0.2">
@@ -581,7 +599,7 @@
         <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>28</v>
@@ -669,7 +687,7 @@
         <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>8</v>
@@ -681,13 +699,13 @@
         <v>24</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>25</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="48" x14ac:dyDescent="0.2">
@@ -698,7 +716,7 @@
         <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>28</v>
